--- a/requirements/handoff/talent/数据导入-生产.xlsx
+++ b/requirements/handoff/talent/数据导入-生产.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13000" activeTab="4"/>
+    <workbookView windowWidth="30240" windowHeight="13000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="人才档案" sheetId="2" r:id="rId1"/>
@@ -32,20 +32,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="126">
   <si>
     <t>姓名</t>
   </si>
   <si>
-    <t>部门</t>
-  </si>
-  <si>
-    <t>小组</t>
-  </si>
-  <si>
-    <t>岗位</t>
-  </si>
-  <si>
     <t>入职日期</t>
   </si>
   <si>
@@ -85,15 +76,6 @@
     <t>詹德锋</t>
   </si>
   <si>
-    <t>产品部</t>
-  </si>
-  <si>
-    <t>B端组</t>
-  </si>
-  <si>
-    <t>产品经理</t>
-  </si>
-  <si>
     <t>R3-3</t>
   </si>
   <si>
@@ -103,9 +85,6 @@
     <t>王俊秀</t>
   </si>
   <si>
-    <t>组长</t>
-  </si>
-  <si>
     <t>R2</t>
   </si>
   <si>
@@ -115,9 +94,6 @@
     <t>李隽贤</t>
   </si>
   <si>
-    <t>采购组</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -133,33 +109,21 @@
     <t>孙圣宇</t>
   </si>
   <si>
-    <t>设计组</t>
-  </si>
-  <si>
     <t>毛博雅</t>
   </si>
   <si>
-    <t>C端组</t>
-  </si>
-  <si>
     <t>谢志健</t>
   </si>
   <si>
     <t>欧阳雯</t>
   </si>
   <si>
-    <t>产品专员</t>
-  </si>
-  <si>
     <t>邓智泳</t>
   </si>
   <si>
     <t>陈小艳</t>
   </si>
   <si>
-    <t>平面设计师</t>
-  </si>
-  <si>
     <t>张永翔</t>
   </si>
   <si>
@@ -169,9 +133,6 @@
     <t>王铭灏</t>
   </si>
   <si>
-    <t>UI设计师</t>
-  </si>
-  <si>
     <t>盘点批次</t>
   </si>
   <si>
@@ -269,12 +230,6 @@
   </si>
   <si>
     <t>2026Q4</t>
-  </si>
-  <si>
-    <t>均值</t>
-  </si>
-  <si>
-    <t>最高分-最低分</t>
   </si>
   <si>
     <t>R3-1-R3-2</t>
@@ -470,13 +425,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -1346,7 +1300,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1557,22 +1511,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1614,7 +1552,7 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2207,22 +2145,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="3" width="8.76923076923077" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.7692307692308" style="3" customWidth="1"/>
-    <col min="5" max="6" width="15.3076923076923" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.2307692307692" style="3" customWidth="1"/>
-    <col min="8" max="12" width="11" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.4615384615385" style="3" customWidth="1"/>
-    <col min="14" max="14" width="19.6153846153846" style="3" customWidth="1"/>
-    <col min="15" max="15" width="18.4615384615385" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.1153846153846" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="3"/>
+    <col min="1" max="1" width="8.76923076923077" style="3" customWidth="1"/>
+    <col min="2" max="3" width="15.3076923076923" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.2307692307692" style="3" customWidth="1"/>
+    <col min="5" max="9" width="11" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.4615384615385" style="3" customWidth="1"/>
+    <col min="11" max="11" width="19.6153846153846" style="3" customWidth="1"/>
+    <col min="12" max="12" width="18.4615384615385" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17.1153846153846" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9.23076923076923" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" spans="1:16">
+    <row r="1" ht="36" spans="1:13">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -2250,559 +2187,424 @@
       <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+    </row>
+    <row r="2" ht="18" spans="1:13">
+      <c r="A2" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="B2" s="56">
+        <v>43297</v>
+      </c>
+      <c r="C2" s="56">
+        <v>45489</v>
+      </c>
+      <c r="D2" s="56">
+        <v>46583</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="F2" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="18" spans="1:16">
-      <c r="A2" s="57" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15">
+        <v>3</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" ht="18" spans="1:13">
+      <c r="A3" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B3" s="56">
+        <v>44368</v>
+      </c>
+      <c r="C3" s="56">
+        <v>45464</v>
+      </c>
+      <c r="D3" s="56">
+        <v>46559</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="F3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15">
+        <v>2</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" ht="18" spans="1:13">
+      <c r="A4" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="58">
-        <v>43297</v>
-      </c>
-      <c r="F2" s="58">
-        <v>45489</v>
-      </c>
-      <c r="G2" s="58">
-        <v>46583</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="B4" s="56">
+        <v>44378</v>
+      </c>
+      <c r="C4" s="56">
+        <v>45474</v>
+      </c>
+      <c r="D4" s="56">
+        <v>46568</v>
+      </c>
+      <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="F4" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15">
-        <v>3</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-    </row>
-    <row r="3" ht="18" spans="1:16">
-      <c r="A3" s="57" t="s">
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15">
+        <v>2</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" ht="18" spans="1:13">
+      <c r="A5" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B5" s="56">
+        <v>44382</v>
+      </c>
+      <c r="C5" s="56">
+        <v>45478</v>
+      </c>
+      <c r="D5" s="56">
+        <v>46572</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15">
+        <v>2</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" ht="18" spans="1:13">
+      <c r="A6" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="56">
+        <v>44522</v>
+      </c>
+      <c r="C6" s="56">
+        <v>45618</v>
+      </c>
+      <c r="D6" s="56">
+        <v>46712</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15">
+        <v>2</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" ht="18" spans="1:13">
+      <c r="A7" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="56">
+        <v>45035</v>
+      </c>
+      <c r="C7" s="56">
+        <v>46131</v>
+      </c>
+      <c r="D7" s="56">
+        <v>47226</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="58">
-        <v>44368</v>
-      </c>
-      <c r="F3" s="58">
-        <v>45464</v>
-      </c>
-      <c r="G3" s="58">
-        <v>46559</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" ht="18" spans="1:13">
+      <c r="A8" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15">
+      <c r="B8" s="56">
+        <v>45078</v>
+      </c>
+      <c r="C8" s="56">
+        <v>46174</v>
+      </c>
+      <c r="D8" s="56">
+        <v>47269</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15">
         <v>2</v>
       </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" ht="18" spans="1:16">
-      <c r="A4" s="57" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" ht="18" spans="1:13">
+      <c r="A9" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B9" s="56">
+        <v>45225</v>
+      </c>
+      <c r="C9" s="56">
+        <v>45225</v>
+      </c>
+      <c r="D9" s="56">
+        <v>46320</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="F9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" ht="18" spans="1:13">
+      <c r="A10" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="58">
-        <v>44378</v>
-      </c>
-      <c r="F4" s="58">
-        <v>45474</v>
-      </c>
-      <c r="G4" s="58">
-        <v>46568</v>
-      </c>
-      <c r="H4" s="59" t="s">
+      <c r="B10" s="56">
+        <v>45323</v>
+      </c>
+      <c r="C10" s="56">
+        <v>45323</v>
+      </c>
+      <c r="D10" s="56">
+        <v>46418</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" ht="18" spans="1:13">
+      <c r="A11" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="B11" s="56">
+        <v>45390</v>
+      </c>
+      <c r="C11" s="56">
+        <v>45390</v>
+      </c>
+      <c r="D11" s="56">
+        <v>46484</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+    </row>
+    <row r="12" ht="18" spans="1:13">
+      <c r="A12" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15">
-        <v>2</v>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-    </row>
-    <row r="5" ht="18" spans="1:16">
-      <c r="A5" s="57" t="s">
+      <c r="B12" s="56">
+        <v>45404</v>
+      </c>
+      <c r="C12" s="56">
+        <v>45404</v>
+      </c>
+      <c r="D12" s="56">
+        <v>46498</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15">
+        <v>1</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" ht="18" spans="1:13">
+      <c r="A13" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="58">
-        <v>44382</v>
-      </c>
-      <c r="F5" s="58">
-        <v>45478</v>
-      </c>
-      <c r="G5" s="58">
-        <v>46572</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15">
-        <v>2</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" ht="18" spans="1:16">
-      <c r="A6" s="57" t="s">
+      <c r="B13" s="56">
+        <v>45544</v>
+      </c>
+      <c r="C13" s="56">
+        <v>45544</v>
+      </c>
+      <c r="D13" s="56">
+        <v>46638</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" ht="18" spans="1:13">
+      <c r="A14" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="58">
-        <v>44522</v>
-      </c>
-      <c r="F6" s="58">
-        <v>45618</v>
-      </c>
-      <c r="G6" s="58">
-        <v>46712</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15">
-        <v>2</v>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-    </row>
-    <row r="7" ht="18" spans="1:16">
-      <c r="A7" s="57" t="s">
+      <c r="B14" s="56">
+        <v>46026</v>
+      </c>
+      <c r="C14" s="56">
+        <v>46026</v>
+      </c>
+      <c r="D14" s="56">
+        <v>47121</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15">
+        <v>1</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" ht="18" spans="1:13">
+      <c r="A15" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="58">
-        <v>45035</v>
-      </c>
-      <c r="F7" s="58">
-        <v>46131</v>
-      </c>
-      <c r="G7" s="58">
-        <v>47226</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15">
-        <v>2</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" ht="18" spans="1:16">
-      <c r="A8" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="58">
-        <v>45078</v>
-      </c>
-      <c r="F8" s="58">
-        <v>46174</v>
-      </c>
-      <c r="G8" s="58">
-        <v>47269</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15">
-        <v>2</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9" ht="18" spans="1:16">
-      <c r="A9" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="58">
-        <v>45225</v>
-      </c>
-      <c r="F9" s="58">
-        <v>45225</v>
-      </c>
-      <c r="G9" s="58">
-        <v>46320</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15">
+      <c r="B15" s="56">
+        <v>46028</v>
+      </c>
+      <c r="C15" s="56">
+        <v>46028</v>
+      </c>
+      <c r="D15" s="56">
+        <v>47123</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15">
         <v>1</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" ht="18" spans="1:16">
-      <c r="A10" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="58">
-        <v>45323</v>
-      </c>
-      <c r="F10" s="58">
-        <v>45323</v>
-      </c>
-      <c r="G10" s="58">
-        <v>46418</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15">
-        <v>1</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-    </row>
-    <row r="11" ht="18" spans="1:16">
-      <c r="A11" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="58">
-        <v>45390</v>
-      </c>
-      <c r="F11" s="58">
-        <v>45390</v>
-      </c>
-      <c r="G11" s="58">
-        <v>46484</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15">
-        <v>1</v>
-      </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" ht="18" spans="1:16">
-      <c r="A12" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="58">
-        <v>45404</v>
-      </c>
-      <c r="F12" s="58">
-        <v>45404</v>
-      </c>
-      <c r="G12" s="58">
-        <v>46498</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" ht="18" spans="1:16">
-      <c r="A13" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="58">
-        <v>45544</v>
-      </c>
-      <c r="F13" s="58">
-        <v>45544</v>
-      </c>
-      <c r="G13" s="58">
-        <v>46638</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15">
-        <v>1</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" ht="18" spans="1:16">
-      <c r="A14" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="58">
-        <v>46026</v>
-      </c>
-      <c r="F14" s="58">
-        <v>46026</v>
-      </c>
-      <c r="G14" s="58">
-        <v>47121</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15">
-        <v>1</v>
-      </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-    </row>
-    <row r="15" ht="18" spans="1:16">
-      <c r="A15" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="58">
-        <v>46028</v>
-      </c>
-      <c r="F15" s="58">
-        <v>46028</v>
-      </c>
-      <c r="G15" s="58">
-        <v>47123</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15">
-        <v>1</v>
-      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
       <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2821,1987 +2623,1987 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:10">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:10">
+      <c r="A2" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="44">
+        <v>21</v>
+      </c>
+      <c r="J2" s="45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="1:10">
+      <c r="A3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="G3" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="47">
+        <v>12</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:10">
+      <c r="A4" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="47">
+        <v>18</v>
+      </c>
+      <c r="J4" s="46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="18" spans="1:10">
+      <c r="A5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="49">
+        <v>12</v>
+      </c>
+      <c r="J5" s="50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="1:10">
+      <c r="A6" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="49">
+        <v>21</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:10">
+      <c r="A7" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="49">
+        <v>14</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:10">
+      <c r="A8" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="44">
+        <v>20</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:10">
+      <c r="A9" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="44">
+        <v>13</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:10">
+      <c r="A10" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="J10" s="52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" ht="18" spans="1:10">
+      <c r="A11" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="44">
+        <v>12</v>
+      </c>
+      <c r="J11" s="53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:10">
+      <c r="A12" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="49">
+        <v>19</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:10">
+      <c r="A13" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="C13" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="54">
+        <v>21</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:10">
+      <c r="A14" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="54">
+        <v>13</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="18" spans="1:10">
+      <c r="A15" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="54">
+        <v>18</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="18" spans="1:10">
+      <c r="A16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="54">
+        <v>14</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:10">
+      <c r="A17" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="54">
+        <v>18</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:10">
+      <c r="A18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="54">
+        <v>22</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:10">
+      <c r="A19" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="54">
+        <v>18</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:10">
+      <c r="A20" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="54">
+        <v>18</v>
+      </c>
+      <c r="J20" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="18" spans="1:10">
+      <c r="A21" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="54">
+        <v>18</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" ht="18" spans="1:10">
+      <c r="A22" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="54">
+        <v>12</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" ht="18" spans="1:10">
+      <c r="A23" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="54">
+        <v>18</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" ht="18" spans="1:10">
+      <c r="A24" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="54">
+        <v>24</v>
+      </c>
+      <c r="J24" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:10">
+      <c r="A25" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="C25" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="54">
+        <v>20</v>
+      </c>
+      <c r="J25" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="18" spans="1:10">
+      <c r="A26" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="54">
+        <v>16</v>
+      </c>
+      <c r="J26" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" ht="18" spans="1:10">
+      <c r="A27" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="54">
+        <v>18</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" ht="18" spans="1:10">
+      <c r="A28" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="54">
+        <v>18</v>
+      </c>
+      <c r="J28" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" ht="18" spans="1:10">
+      <c r="A29" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="54">
+        <v>18</v>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" ht="18" spans="1:10">
+      <c r="A30" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="54">
+        <v>22</v>
+      </c>
+      <c r="J30" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" ht="18" spans="1:10">
+      <c r="A31" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" s="54">
+        <v>19</v>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="18" spans="1:10">
+      <c r="A32" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="54">
+        <v>21</v>
+      </c>
+      <c r="J32" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" ht="18" spans="1:10">
+      <c r="A33" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="54">
+        <v>19</v>
+      </c>
+      <c r="J33" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" ht="18" spans="1:10">
+      <c r="A34" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="54">
+        <v>12</v>
+      </c>
+      <c r="J34" s="41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" ht="18" spans="1:10">
+      <c r="A35" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="54">
+        <v>16</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" ht="18" spans="1:10">
+      <c r="A36" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="54">
+        <v>20</v>
+      </c>
+      <c r="J36" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" ht="18" spans="1:10">
+      <c r="A37" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="C37" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="54">
+        <v>19</v>
+      </c>
+      <c r="J37" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" ht="18" spans="1:10">
+      <c r="A38" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G38" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="54">
+        <v>17</v>
+      </c>
+      <c r="J38" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" ht="18" spans="1:10">
+      <c r="A39" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I39" s="54">
+        <v>18</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" ht="18" spans="1:10">
+      <c r="A40" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="54">
+        <v>22</v>
+      </c>
+      <c r="J40" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" ht="18" spans="1:10">
+      <c r="A41" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="54">
+        <v>18</v>
+      </c>
+      <c r="J41" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" ht="18" spans="1:10">
+      <c r="A42" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="54">
+        <v>21</v>
+      </c>
+      <c r="J42" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" ht="18" spans="1:10">
+      <c r="A43" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="54">
+        <v>18</v>
+      </c>
+      <c r="J43" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" ht="18" spans="1:10">
+      <c r="A44" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="54">
+        <v>18</v>
+      </c>
+      <c r="J44" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" ht="18" spans="1:10">
+      <c r="A45" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I45" s="54">
+        <v>19</v>
+      </c>
+      <c r="J45" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" ht="18" spans="1:10">
+      <c r="A46" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I46" s="54">
+        <v>14</v>
+      </c>
+      <c r="J46" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" ht="18" spans="1:10">
+      <c r="A47" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H47" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I47" s="54">
+        <v>17</v>
+      </c>
+      <c r="J47" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" ht="18" spans="1:10">
+      <c r="A48" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I48" s="54">
+        <v>19</v>
+      </c>
+      <c r="J48" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" ht="18" spans="1:10">
+      <c r="A49" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="C49" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H49" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" s="54">
+        <v>19</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" ht="18" spans="1:10">
+      <c r="A50" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H50" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" s="54">
+        <v>18</v>
+      </c>
+      <c r="J50" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" ht="18" spans="1:10">
+      <c r="A51" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H51" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I51" s="54">
+        <v>19</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" ht="18" spans="1:10">
+      <c r="A52" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="54">
+        <v>23</v>
+      </c>
+      <c r="J52" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" ht="18" spans="1:10">
+      <c r="A53" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:10">
-      <c r="A2" s="43" t="s">
+      <c r="E53" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H53" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I53" s="54">
+        <v>24</v>
+      </c>
+      <c r="J53" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" ht="18" spans="1:10">
+      <c r="A54" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I54" s="54">
+        <v>21</v>
+      </c>
+      <c r="J54" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" ht="18" spans="1:10">
+      <c r="A55" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H55" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I55" s="54">
+        <v>21</v>
+      </c>
+      <c r="J55" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" ht="18" spans="1:10">
+      <c r="A56" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H56" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I56" s="54">
+        <v>18</v>
+      </c>
+      <c r="J56" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" ht="18" spans="1:10">
+      <c r="A57" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H57" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="54">
+        <v>20</v>
+      </c>
+      <c r="J57" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" ht="18" spans="1:10">
+      <c r="A58" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H58" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" s="54">
+        <v>12</v>
+      </c>
+      <c r="J58" s="41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" ht="18" spans="1:10">
+      <c r="A59" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I59" s="54">
+        <v>19</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" ht="18" spans="1:10">
+      <c r="A60" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="54">
+        <v>15</v>
+      </c>
+      <c r="J60" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" ht="18" spans="1:10">
+      <c r="A61" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="46">
-        <v>21</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" ht="18" spans="1:10">
-      <c r="A3" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="49">
-        <v>12</v>
-      </c>
-      <c r="J3" s="48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" ht="18" spans="1:10">
-      <c r="A4" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="49">
+      <c r="B61" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I61" s="54">
         <v>18</v>
       </c>
-      <c r="J4" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" ht="18" spans="1:10">
-      <c r="A5" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="51">
-        <v>12</v>
-      </c>
-      <c r="J5" s="52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" ht="18" spans="1:10">
-      <c r="A6" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="51">
-        <v>21</v>
-      </c>
-      <c r="J6" s="51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:10">
-      <c r="A7" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="51">
-        <v>14</v>
-      </c>
-      <c r="J7" s="51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:10">
-      <c r="A8" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="46">
+      <c r="J61" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" ht="18" spans="1:10">
+      <c r="A62" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C62" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E62" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G62" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="I62" s="54">
         <v>20</v>
       </c>
-      <c r="J8" s="45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" ht="18" spans="1:10">
-      <c r="A9" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="46">
-        <v>13</v>
-      </c>
-      <c r="J9" s="47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:10">
-      <c r="A10" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" ht="18" spans="1:10">
-      <c r="A11" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="46">
-        <v>12</v>
-      </c>
-      <c r="J11" s="55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" ht="18" spans="1:10">
-      <c r="A12" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="51">
-        <v>19</v>
-      </c>
-      <c r="J12" s="51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:10">
-      <c r="A13" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" s="56">
-        <v>21</v>
-      </c>
-      <c r="J13" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:10">
-      <c r="A14" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="56">
-        <v>13</v>
-      </c>
-      <c r="J14" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" ht="18" spans="1:10">
-      <c r="A15" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="56">
-        <v>18</v>
-      </c>
-      <c r="J15" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" ht="18" spans="1:10">
-      <c r="A16" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="56">
-        <v>14</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" ht="18" spans="1:10">
-      <c r="A17" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="56">
-        <v>18</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:10">
-      <c r="A18" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="56">
-        <v>22</v>
-      </c>
-      <c r="J18" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:10">
-      <c r="A19" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="56">
-        <v>18</v>
-      </c>
-      <c r="J19" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:10">
-      <c r="A20" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I20" s="56">
-        <v>18</v>
-      </c>
-      <c r="J20" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" ht="18" spans="1:10">
-      <c r="A21" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="56">
-        <v>18</v>
-      </c>
-      <c r="J21" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" ht="18" spans="1:10">
-      <c r="A22" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="56">
-        <v>12</v>
-      </c>
-      <c r="J22" s="43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:10">
-      <c r="A23" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23" s="56">
-        <v>18</v>
-      </c>
-      <c r="J23" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:10">
-      <c r="A24" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" s="56">
-        <v>24</v>
-      </c>
-      <c r="J24" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:10">
-      <c r="A25" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I25" s="56">
-        <v>20</v>
-      </c>
-      <c r="J25" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" ht="18" spans="1:10">
-      <c r="A26" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I26" s="56">
-        <v>16</v>
-      </c>
-      <c r="J26" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" ht="18" spans="1:10">
-      <c r="A27" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="56">
-        <v>18</v>
-      </c>
-      <c r="J27" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" ht="18" spans="1:10">
-      <c r="A28" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H28" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="56">
-        <v>18</v>
-      </c>
-      <c r="J28" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" ht="18" spans="1:10">
-      <c r="A29" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H29" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" s="56">
-        <v>18</v>
-      </c>
-      <c r="J29" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" ht="18" spans="1:10">
-      <c r="A30" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="56">
-        <v>22</v>
-      </c>
-      <c r="J30" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" ht="18" spans="1:10">
-      <c r="A31" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I31" s="56">
-        <v>19</v>
-      </c>
-      <c r="J31" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" ht="18" spans="1:10">
-      <c r="A32" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I32" s="56">
-        <v>21</v>
-      </c>
-      <c r="J32" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" ht="18" spans="1:10">
-      <c r="A33" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I33" s="56">
-        <v>19</v>
-      </c>
-      <c r="J33" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" ht="18" spans="1:10">
-      <c r="A34" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H34" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I34" s="56">
-        <v>12</v>
-      </c>
-      <c r="J34" s="43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" ht="18" spans="1:10">
-      <c r="A35" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I35" s="56">
-        <v>16</v>
-      </c>
-      <c r="J35" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" ht="18" spans="1:10">
-      <c r="A36" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I36" s="56">
-        <v>20</v>
-      </c>
-      <c r="J36" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" ht="18" spans="1:10">
-      <c r="A37" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" s="56">
-        <v>19</v>
-      </c>
-      <c r="J37" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" ht="18" spans="1:10">
-      <c r="A38" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" s="56">
-        <v>17</v>
-      </c>
-      <c r="J38" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" ht="18" spans="1:10">
-      <c r="A39" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G39" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I39" s="56">
-        <v>18</v>
-      </c>
-      <c r="J39" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" ht="18" spans="1:10">
-      <c r="A40" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I40" s="56">
-        <v>22</v>
-      </c>
-      <c r="J40" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" ht="18" spans="1:10">
-      <c r="A41" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F41" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I41" s="56">
-        <v>18</v>
-      </c>
-      <c r="J41" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" ht="18" spans="1:10">
-      <c r="A42" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F42" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H42" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I42" s="56">
-        <v>21</v>
-      </c>
-      <c r="J42" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" ht="18" spans="1:10">
-      <c r="A43" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F43" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" s="56">
-        <v>18</v>
-      </c>
-      <c r="J43" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" ht="18" spans="1:10">
-      <c r="A44" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H44" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I44" s="56">
-        <v>18</v>
-      </c>
-      <c r="J44" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" ht="18" spans="1:10">
-      <c r="A45" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F45" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H45" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I45" s="56">
-        <v>19</v>
-      </c>
-      <c r="J45" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" ht="18" spans="1:10">
-      <c r="A46" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G46" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H46" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I46" s="56">
-        <v>14</v>
-      </c>
-      <c r="J46" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" ht="18" spans="1:10">
-      <c r="A47" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F47" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H47" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I47" s="56">
-        <v>17</v>
-      </c>
-      <c r="J47" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" ht="18" spans="1:10">
-      <c r="A48" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F48" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G48" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H48" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I48" s="56">
-        <v>19</v>
-      </c>
-      <c r="J48" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" ht="18" spans="1:10">
-      <c r="A49" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G49" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H49" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I49" s="56">
-        <v>19</v>
-      </c>
-      <c r="J49" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" ht="18" spans="1:10">
-      <c r="A50" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G50" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H50" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I50" s="56">
-        <v>18</v>
-      </c>
-      <c r="J50" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" ht="18" spans="1:10">
-      <c r="A51" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B51" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G51" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H51" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I51" s="56">
-        <v>19</v>
-      </c>
-      <c r="J51" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" ht="18" spans="1:10">
-      <c r="A52" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G52" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H52" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I52" s="56">
-        <v>23</v>
-      </c>
-      <c r="J52" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" ht="18" spans="1:10">
-      <c r="A53" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G53" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H53" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I53" s="56">
-        <v>24</v>
-      </c>
-      <c r="J53" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" ht="18" spans="1:10">
-      <c r="A54" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E54" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G54" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H54" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I54" s="56">
-        <v>21</v>
-      </c>
-      <c r="J54" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" ht="18" spans="1:10">
-      <c r="A55" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E55" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="G55" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H55" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I55" s="56">
-        <v>21</v>
-      </c>
-      <c r="J55" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" ht="18" spans="1:10">
-      <c r="A56" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C56" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F56" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G56" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H56" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I56" s="56">
-        <v>18</v>
-      </c>
-      <c r="J56" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" ht="18" spans="1:10">
-      <c r="A57" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D57" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G57" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I57" s="56">
-        <v>20</v>
-      </c>
-      <c r="J57" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" ht="18" spans="1:10">
-      <c r="A58" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B58" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H58" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="I58" s="56">
-        <v>12</v>
-      </c>
-      <c r="J58" s="43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" ht="18" spans="1:10">
-      <c r="A59" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B59" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D59" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E59" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F59" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G59" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H59" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I59" s="56">
-        <v>19</v>
-      </c>
-      <c r="J59" s="43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="60" ht="18" spans="1:10">
-      <c r="A60" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E60" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F60" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G60" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H60" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I60" s="56">
-        <v>15</v>
-      </c>
-      <c r="J60" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" ht="18" spans="1:10">
-      <c r="A61" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B61" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H61" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="I61" s="56">
-        <v>18</v>
-      </c>
-      <c r="J61" s="43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" ht="18" spans="1:10">
-      <c r="A62" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="E62" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F62" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="G62" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="H62" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I62" s="56">
-        <v>20</v>
-      </c>
-      <c r="J62" s="43" t="s">
-        <v>56</v>
+      <c r="J62" s="41" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4813,7 +4615,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="15.9230769230769" style="3" customWidth="1"/>
@@ -4824,48 +4626,48 @@
   <sheetData>
     <row r="1" ht="18" spans="1:13">
       <c r="A1" s="27" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K1" s="27" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="M1" s="29" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
       <c r="A2" s="30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" s="31">
         <v>102</v>
@@ -4902,7 +4704,7 @@
     </row>
     <row r="3" ht="18" spans="1:13">
       <c r="A3" s="30" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B3" s="36">
         <v>105</v>
@@ -4939,7 +4741,7 @@
     </row>
     <row r="4" ht="18" spans="1:13">
       <c r="A4" s="30" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4" s="36">
         <v>100</v>
@@ -4976,7 +4778,7 @@
     </row>
     <row r="5" ht="18" spans="1:13">
       <c r="A5" s="30" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B5" s="36">
         <v>100</v>
@@ -5013,7 +4815,7 @@
     </row>
     <row r="6" ht="18" spans="1:13">
       <c r="A6" s="30" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6" s="36">
         <v>100</v>
@@ -5050,7 +4852,7 @@
     </row>
     <row r="7" ht="18" spans="1:13">
       <c r="A7" s="30" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B7" s="36">
         <v>102.5</v>
@@ -5087,7 +4889,7 @@
     </row>
     <row r="8" ht="18" spans="1:13">
       <c r="A8" s="30" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" s="36">
         <v>98</v>
@@ -5124,7 +4926,7 @@
     </row>
     <row r="9" ht="18" spans="1:13">
       <c r="A9" s="30" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B9" s="36">
         <v>100</v>
@@ -5161,7 +4963,7 @@
     </row>
     <row r="10" ht="18" spans="1:13">
       <c r="A10" s="30" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B10" s="36">
         <v>95</v>
@@ -5198,7 +5000,7 @@
     </row>
     <row r="11" ht="18" spans="1:13">
       <c r="A11" s="30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="37">
@@ -5233,7 +5035,7 @@
     </row>
     <row r="12" ht="18" spans="1:13">
       <c r="A12" s="30" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="37">
@@ -5268,7 +5070,7 @@
     </row>
     <row r="13" ht="18" spans="1:13">
       <c r="A13" s="30" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13" s="36"/>
       <c r="C13" s="37"/>
@@ -5299,7 +5101,7 @@
     </row>
     <row r="14" ht="18" spans="1:13">
       <c r="A14" s="30" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="37"/>
@@ -5320,7 +5122,7 @@
     </row>
     <row r="15" ht="18" spans="1:13">
       <c r="A15" s="30" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B15" s="36"/>
       <c r="C15" s="37"/>
@@ -5338,56 +5140,6 @@
       </c>
       <c r="L15" s="35"/>
       <c r="M15" s="15"/>
-    </row>
-    <row r="16" ht="18" spans="1:13">
-      <c r="A16" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="41">
-        <f>AVERAGE(B2:B15)</f>
-        <v>100.277777777778</v>
-      </c>
-      <c r="C16" s="41">
-        <f t="shared" ref="C16:K16" si="0">AVERAGE(C2:C15)</f>
-        <v>99</v>
-      </c>
-      <c r="D16" s="41">
-        <f>AVERAGE(D2:D15)</f>
-        <v>99.7272727272727</v>
-      </c>
-      <c r="E16" s="41">
-        <f t="shared" si="0"/>
-        <v>99.5416666666667</v>
-      </c>
-      <c r="F16" s="41">
-        <f t="shared" si="0"/>
-        <v>100.25</v>
-      </c>
-      <c r="G16" s="41">
-        <f t="shared" si="0"/>
-        <v>99.7083333333333</v>
-      </c>
-      <c r="H16" s="41">
-        <f t="shared" si="0"/>
-        <v>99.7916666666667</v>
-      </c>
-      <c r="I16" s="41">
-        <f t="shared" si="0"/>
-        <v>99.0416666666667</v>
-      </c>
-      <c r="J16" s="41">
-        <f t="shared" si="0"/>
-        <v>98.7857142857143</v>
-      </c>
-      <c r="K16" s="41">
-        <f t="shared" si="0"/>
-        <v>100.271428571429</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5412,30 +5164,30 @@
   <sheetData>
     <row r="1" s="24" customFormat="1" ht="18" spans="1:7">
       <c r="A1" s="25" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" s="24" customFormat="1" spans="1:7">
       <c r="A2" s="25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -5446,12 +5198,12 @@
     </row>
     <row r="3" s="24" customFormat="1" spans="1:7">
       <c r="A3" s="25" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
@@ -5459,12 +5211,12 @@
     </row>
     <row r="4" s="24" customFormat="1" spans="1:7">
       <c r="A4" s="25" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
       <c r="D4" s="22" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
@@ -5472,10 +5224,10 @@
     </row>
     <row r="5" s="24" customFormat="1" spans="1:7">
       <c r="A5" s="25" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -5485,24 +5237,24 @@
     </row>
     <row r="6" s="24" customFormat="1" spans="1:7">
       <c r="A6" s="25" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G6" s="22"/>
     </row>
     <row r="7" s="24" customFormat="1" spans="1:7">
       <c r="A7" s="25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
@@ -5511,33 +5263,33 @@
     </row>
     <row r="8" s="24" customFormat="1" spans="1:7">
       <c r="A8" s="25" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
     </row>
     <row r="9" s="24" customFormat="1" spans="1:7">
       <c r="A9" s="25" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
     </row>
     <row r="10" s="24" customFormat="1" spans="1:7">
       <c r="A10" s="25" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -5548,7 +5300,7 @@
     </row>
     <row r="11" s="24" customFormat="1" spans="1:7">
       <c r="A11" s="25" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -5559,20 +5311,20 @@
     </row>
     <row r="12" s="24" customFormat="1" spans="1:7">
       <c r="A12" s="25" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="22" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G12" s="22"/>
     </row>
     <row r="13" s="24" customFormat="1" spans="1:7">
       <c r="A13" s="25" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -5583,7 +5335,7 @@
     </row>
     <row r="14" s="24" customFormat="1" spans="1:7">
       <c r="A14" s="25" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -5594,7 +5346,7 @@
     </row>
     <row r="15" s="24" customFormat="1" spans="1:7">
       <c r="A15" s="25" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -5621,25 +5373,25 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="17" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="19"/>
       <c r="B2" s="18" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="21">
         <v>44393</v>
@@ -5650,7 +5402,7 @@
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="21">
         <v>45489</v>
@@ -5661,7 +5413,7 @@
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="20" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B5" s="21">
         <v>45464</v>
@@ -5672,7 +5424,7 @@
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="20" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" s="21">
         <v>45474</v>
@@ -5683,7 +5435,7 @@
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="20" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B7" s="21">
         <v>45478</v>
@@ -5694,7 +5446,7 @@
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="20" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8" s="21">
         <v>45618</v>
@@ -5705,7 +5457,7 @@
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9" s="21">
         <v>46131</v>
@@ -5716,7 +5468,7 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B10" s="21">
         <v>46174</v>
@@ -5795,14 +5547,14 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.4" spans="1:19">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="7" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -5820,76 +5572,76 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="36" spans="1:19">
       <c r="A2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="Q2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="R2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A3" s="12" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -5905,55 +5657,55 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A4" s="12" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G4" s="9">
         <v>110</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -5961,47 +5713,47 @@
     </row>
     <row r="5" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A5" s="12" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G5" s="9">
         <v>110</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -6010,47 +5762,47 @@
     </row>
     <row r="6" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A6" s="12" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G6" s="9">
         <v>40</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -6059,43 +5811,43 @@
     </row>
     <row r="7" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A7" s="12" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G7" s="9">
         <v>10</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -6104,43 +5856,43 @@
     </row>
     <row r="8" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A8" s="14" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -6149,62 +5901,62 @@
     </row>
     <row r="9" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A9" s="14" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="18" spans="1:19">
       <c r="A10" s="16" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -6220,48 +5972,48 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A11" s="16" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -6270,17 +6022,17 @@
     </row>
     <row r="12" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A12" s="16" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -6296,22 +6048,22 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A13" s="16" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
@@ -6327,22 +6079,22 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" ht="53" spans="1:19">
       <c r="A14" s="16" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -6358,22 +6110,22 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A15" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -6389,22 +6141,22 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="36" spans="1:19">
       <c r="A16" s="16" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -6420,7 +6172,7 @@
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
       <c r="S16" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/requirements/handoff/talent/数据导入-生产.xlsx
+++ b/requirements/handoff/talent/数据导入-生产.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12940" activeTab="6"/>
+    <workbookView windowWidth="30240" windowHeight="12940" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="人才档案" sheetId="2" r:id="rId1"/>

--- a/requirements/handoff/talent/数据导入-生产.xlsx
+++ b/requirements/handoff/talent/数据导入-生产.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12940" activeTab="5"/>
+    <workbookView windowWidth="30240" windowHeight="12940" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="人才档案" sheetId="2" r:id="rId1"/>
@@ -1264,7 +1264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1319,6 +1319,12 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
@@ -1332,9 +1338,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2169,451 +2172,451 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" spans="1:13">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="L1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="58" t="s">
+      <c r="M1" s="59" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="60">
+      <c r="B2" s="61">
         <v>43297</v>
       </c>
-      <c r="C2" s="60">
+      <c r="C2" s="61">
         <v>45489</v>
       </c>
-      <c r="D2" s="60">
+      <c r="D2" s="61">
         <v>46583</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40">
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41">
         <v>3</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
     </row>
     <row r="3" ht="18" spans="1:13">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="61">
         <v>44368</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="61">
         <v>45464</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="61">
         <v>46559</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40">
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41">
         <v>2</v>
       </c>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
     </row>
     <row r="4" ht="18" spans="1:13">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="61">
         <v>44378</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="61">
         <v>45474</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="61">
         <v>46568</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40">
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41">
         <v>2</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
     </row>
     <row r="5" ht="18" spans="1:13">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="61">
         <v>44382</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="61">
         <v>45478</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="61">
         <v>46572</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40">
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41">
         <v>2</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
     </row>
     <row r="6" ht="18" spans="1:13">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="61">
         <v>44522</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="61">
         <v>45618</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="61">
         <v>46712</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40">
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41">
         <v>2</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
     </row>
     <row r="7" ht="18" spans="1:13">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="61">
         <v>45035</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="61">
         <v>46131</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="61">
         <v>47226</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40">
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41">
         <v>2</v>
       </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
     </row>
     <row r="8" ht="18" spans="1:13">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="61">
         <v>45078</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="61">
         <v>46174</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="61">
         <v>47269</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40">
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41">
         <v>2</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
     </row>
     <row r="9" ht="18" spans="1:13">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="61">
         <v>45225</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="61">
         <v>45225</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="61">
         <v>46320</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40">
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41">
         <v>1</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
     </row>
     <row r="10" ht="18" spans="1:13">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="61">
         <v>45323</v>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="61">
         <v>45323</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="61">
         <v>46418</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40">
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41">
         <v>1</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
     </row>
     <row r="11" ht="18" spans="1:13">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="61">
         <v>45390</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="61">
         <v>45390</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="61">
         <v>46484</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40">
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41">
         <v>1</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
     </row>
     <row r="12" ht="18" spans="1:13">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="61">
         <v>45404</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="61">
         <v>45404</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="61">
         <v>46498</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40">
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41">
         <v>1</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
     </row>
     <row r="13" ht="18" spans="1:13">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="61">
         <v>45544</v>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="61">
         <v>45544</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="61">
         <v>46638</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40">
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41">
         <v>1</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
     </row>
     <row r="14" ht="18" spans="1:13">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="61">
         <v>46026</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="61">
         <v>46026</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="61">
         <v>47121</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40">
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41">
         <v>1</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
     </row>
     <row r="15" ht="18" spans="1:13">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="60">
+      <c r="B15" s="61">
         <v>46028</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="61">
         <v>46028</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="61">
         <v>47123</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41">
         <v>1</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2632,2172 +2635,2172 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:11">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="K1" s="46" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="48">
         <v>45473</v>
       </c>
-      <c r="D2" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="50">
+      <c r="D2" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="51">
         <v>21</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="51" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:11">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="48">
         <v>45473</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="D3" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="52">
+      <c r="H3" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="53">
         <v>12</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="52" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:11">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="48">
         <v>45473</v>
       </c>
-      <c r="D4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="52">
+      <c r="D4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="53">
         <v>18</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="52" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:11">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="48">
         <v>45473</v>
       </c>
-      <c r="D5" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="53" t="s">
+      <c r="D5" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="54">
+      <c r="H5" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="55">
         <v>12</v>
       </c>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="56" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:11">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="48">
         <v>45473</v>
       </c>
-      <c r="D6" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="54">
+      <c r="D6" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="55">
         <v>21</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="55" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:11">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="48">
         <v>45473</v>
       </c>
-      <c r="D7" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="54">
+      <c r="D7" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="55">
         <v>14</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="55" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:11">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="48">
         <v>45473</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="50">
+      <c r="D8" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="51">
         <v>20</v>
       </c>
-      <c r="K8" s="49" t="s">
+      <c r="K8" s="50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:11">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="48">
         <v>45473</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="50">
+      <c r="D9" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="51">
         <v>13</v>
       </c>
-      <c r="K9" s="50" t="s">
+      <c r="K9" s="51" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:11">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="48">
         <v>45473</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="45" t="s">
+      <c r="D10" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="45" t="s">
+      <c r="J10" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="45" t="s">
+      <c r="K10" s="46" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:11">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="48">
         <v>45473</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="48" t="s">
+      <c r="D11" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="50">
+      <c r="H11" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="51">
         <v>12</v>
       </c>
-      <c r="K11" s="57" t="s">
+      <c r="K11" s="58" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:11">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="48">
         <v>45473</v>
       </c>
-      <c r="D12" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="54">
+      <c r="D12" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="55">
         <v>19</v>
       </c>
-      <c r="K12" s="54" t="s">
+      <c r="K12" s="55" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:11">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="48">
         <v>45657</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="46">
+      <c r="D13" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="47">
         <v>21</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:11">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="48">
         <v>45657</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="46">
+      <c r="D14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="47">
         <v>13</v>
       </c>
-      <c r="K14" s="46" t="s">
+      <c r="K14" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:11">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="48">
         <v>45657</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="46">
+      <c r="D15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="47">
         <v>18</v>
       </c>
-      <c r="K15" s="46" t="s">
+      <c r="K15" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:11">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="48">
         <v>45657</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="46">
+      <c r="D16" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="47">
         <v>14</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:11">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="48">
         <v>45657</v>
       </c>
-      <c r="D17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="46">
+      <c r="D17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="47">
         <v>18</v>
       </c>
-      <c r="K17" s="46" t="s">
+      <c r="K17" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:11">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="48">
         <v>45657</v>
       </c>
-      <c r="D18" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="46">
+      <c r="D18" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="47">
         <v>22</v>
       </c>
-      <c r="K18" s="46" t="s">
+      <c r="K18" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:11">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="48">
         <v>45657</v>
       </c>
-      <c r="D19" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="46">
+      <c r="D19" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="47">
         <v>18</v>
       </c>
-      <c r="K19" s="46" t="s">
+      <c r="K19" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:11">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="48">
         <v>45657</v>
       </c>
-      <c r="D20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20" s="46">
+      <c r="D20" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20" s="47">
         <v>18</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:11">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="48">
         <v>45657</v>
       </c>
-      <c r="D21" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="46">
+      <c r="D21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="47">
         <v>18</v>
       </c>
-      <c r="K21" s="46" t="s">
+      <c r="K21" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:11">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="48">
         <v>45657</v>
       </c>
-      <c r="D22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="46">
+      <c r="D22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="47">
         <v>12</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:11">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="48">
         <v>45657</v>
       </c>
-      <c r="D23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="46">
+      <c r="D23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="47">
         <v>18</v>
       </c>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:11">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="48">
         <v>45657</v>
       </c>
-      <c r="D24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="46">
+      <c r="D24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="47">
         <v>24</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:11">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="48">
         <v>45838</v>
       </c>
-      <c r="D25" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="46">
+      <c r="D25" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="47">
         <v>20</v>
       </c>
-      <c r="K25" s="46" t="s">
+      <c r="K25" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:11">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="48">
         <v>45838</v>
       </c>
-      <c r="D26" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H26" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" s="46">
+      <c r="D26" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="47">
         <v>16</v>
       </c>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:11">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="48">
         <v>45838</v>
       </c>
-      <c r="D27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27" s="46">
+      <c r="D27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" s="47">
         <v>18</v>
       </c>
-      <c r="K27" s="46" t="s">
+      <c r="K27" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:11">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="48">
         <v>45838</v>
       </c>
-      <c r="D28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" s="46">
+      <c r="D28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="47">
         <v>18</v>
       </c>
-      <c r="K28" s="46" t="s">
+      <c r="K28" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:11">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="48">
         <v>45838</v>
       </c>
-      <c r="D29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J29" s="46">
+      <c r="D29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" s="47">
         <v>18</v>
       </c>
-      <c r="K29" s="46" t="s">
+      <c r="K29" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:11">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="48">
         <v>45838</v>
       </c>
-      <c r="D30" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" s="46">
+      <c r="D30" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="47">
         <v>22</v>
       </c>
-      <c r="K30" s="46" t="s">
+      <c r="K30" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:11">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="48">
         <v>45838</v>
       </c>
-      <c r="D31" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I31" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="46">
+      <c r="D31" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="47">
         <v>19</v>
       </c>
-      <c r="K31" s="46" t="s">
+      <c r="K31" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:11">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="48">
         <v>45838</v>
       </c>
-      <c r="D32" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="46">
+      <c r="D32" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="47">
         <v>21</v>
       </c>
-      <c r="K32" s="46" t="s">
+      <c r="K32" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:11">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="48">
         <v>45838</v>
       </c>
-      <c r="D33" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="46">
+      <c r="D33" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="47">
         <v>19</v>
       </c>
-      <c r="K33" s="46" t="s">
+      <c r="K33" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:11">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="48">
         <v>45838</v>
       </c>
-      <c r="D34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" s="46">
+      <c r="D34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" s="47">
         <v>12</v>
       </c>
-      <c r="K34" s="46" t="s">
+      <c r="K34" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:11">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="48">
         <v>45838</v>
       </c>
-      <c r="D35" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H35" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J35" s="46">
+      <c r="D35" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" s="47">
         <v>16</v>
       </c>
-      <c r="K35" s="46" t="s">
+      <c r="K35" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:11">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="48">
         <v>45838</v>
       </c>
-      <c r="D36" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G36" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" s="46">
+      <c r="D36" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="47">
         <v>20</v>
       </c>
-      <c r="K36" s="46" t="s">
+      <c r="K36" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:11">
-      <c r="A37" s="46" t="s">
+      <c r="A37" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="48">
         <v>46022</v>
       </c>
-      <c r="D37" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G37" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J37" s="46">
+      <c r="D37" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J37" s="47">
         <v>19</v>
       </c>
-      <c r="K37" s="46" t="s">
+      <c r="K37" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:11">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="48">
         <v>46022</v>
       </c>
-      <c r="D38" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H38" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I38" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J38" s="46">
+      <c r="D38" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" s="47">
         <v>17</v>
       </c>
-      <c r="K38" s="46" t="s">
+      <c r="K38" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:11">
-      <c r="A39" s="46" t="s">
+      <c r="A39" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="48">
         <v>46022</v>
       </c>
-      <c r="D39" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G39" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I39" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J39" s="46">
+      <c r="D39" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J39" s="47">
         <v>18</v>
       </c>
-      <c r="K39" s="46" t="s">
+      <c r="K39" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:11">
-      <c r="A40" s="46" t="s">
+      <c r="A40" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="46" t="s">
+      <c r="B40" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="48">
         <v>46022</v>
       </c>
-      <c r="D40" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H40" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J40" s="46">
+      <c r="D40" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="47">
         <v>22</v>
       </c>
-      <c r="K40" s="46" t="s">
+      <c r="K40" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:11">
-      <c r="A41" s="46" t="s">
+      <c r="A41" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="46" t="s">
+      <c r="B41" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="48">
         <v>46022</v>
       </c>
-      <c r="D41" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G41" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H41" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I41" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J41" s="46">
+      <c r="D41" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I41" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="47">
         <v>18</v>
       </c>
-      <c r="K41" s="46" t="s">
+      <c r="K41" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:11">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="48">
         <v>46022</v>
       </c>
-      <c r="D42" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G42" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J42" s="46">
+      <c r="D42" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" s="47">
         <v>21</v>
       </c>
-      <c r="K42" s="46" t="s">
+      <c r="K42" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:11">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="48">
         <v>46022</v>
       </c>
-      <c r="D43" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G43" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H43" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J43" s="46">
+      <c r="D43" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" s="47">
         <v>18</v>
       </c>
-      <c r="K43" s="46" t="s">
+      <c r="K43" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:11">
-      <c r="A44" s="46" t="s">
+      <c r="A44" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="48">
         <v>46022</v>
       </c>
-      <c r="D44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I44" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J44" s="46">
+      <c r="D44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" s="47">
         <v>18</v>
       </c>
-      <c r="K44" s="46" t="s">
+      <c r="K44" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:11">
-      <c r="A45" s="46" t="s">
+      <c r="A45" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="48">
         <v>46022</v>
       </c>
-      <c r="D45" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E45" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G45" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J45" s="46">
+      <c r="D45" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="47">
         <v>19</v>
       </c>
-      <c r="K45" s="46" t="s">
+      <c r="K45" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:11">
-      <c r="A46" s="46" t="s">
+      <c r="A46" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="46" t="s">
+      <c r="B46" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="48">
         <v>46022</v>
       </c>
-      <c r="D46" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E46" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G46" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H46" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="46">
+      <c r="D46" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="47">
         <v>14</v>
       </c>
-      <c r="K46" s="46" t="s">
+      <c r="K46" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:11">
-      <c r="A47" s="46" t="s">
+      <c r="A47" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="48">
         <v>46022</v>
       </c>
-      <c r="D47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G47" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I47" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J47" s="46">
+      <c r="D47" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J47" s="47">
         <v>17</v>
       </c>
-      <c r="K47" s="46" t="s">
+      <c r="K47" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:11">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="47">
+      <c r="C48" s="48">
         <v>46022</v>
       </c>
-      <c r="D48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I48" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J48" s="46">
+      <c r="D48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I48" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J48" s="47">
         <v>19</v>
       </c>
-      <c r="K48" s="46" t="s">
+      <c r="K48" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:11">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <v>46203</v>
       </c>
-      <c r="D49" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G49" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H49" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I49" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J49" s="46">
+      <c r="D49" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G49" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" s="47">
         <v>19</v>
       </c>
-      <c r="K49" s="46" t="s">
+      <c r="K49" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:11">
-      <c r="A50" s="46" t="s">
+      <c r="A50" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="47">
+      <c r="C50" s="48">
         <v>46203</v>
       </c>
-      <c r="D50" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G50" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H50" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I50" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J50" s="46">
+      <c r="D50" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J50" s="47">
         <v>18</v>
       </c>
-      <c r="K50" s="46" t="s">
+      <c r="K50" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:11">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="46" t="s">
+      <c r="B51" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="47">
+      <c r="C51" s="48">
         <v>46203</v>
       </c>
-      <c r="D51" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G51" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H51" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I51" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J51" s="46">
+      <c r="D51" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G51" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I51" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J51" s="47">
         <v>19</v>
       </c>
-      <c r="K51" s="46" t="s">
+      <c r="K51" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:11">
-      <c r="A52" s="46" t="s">
+      <c r="A52" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="47">
+      <c r="C52" s="48">
         <v>46203</v>
       </c>
-      <c r="D52" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F52" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H52" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I52" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J52" s="46">
+      <c r="D52" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I52" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" s="47">
         <v>23</v>
       </c>
-      <c r="K52" s="46" t="s">
+      <c r="K52" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:11">
-      <c r="A53" s="46" t="s">
+      <c r="A53" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="46" t="s">
+      <c r="B53" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="47">
+      <c r="C53" s="48">
         <v>46203</v>
       </c>
-      <c r="D53" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="46" t="s">
+      <c r="D53" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="F53" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G53" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H53" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I53" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J53" s="46">
+      <c r="F53" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H53" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I53" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J53" s="47">
         <v>24</v>
       </c>
-      <c r="K53" s="46" t="s">
+      <c r="K53" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:11">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="46" t="s">
+      <c r="B54" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="47">
+      <c r="C54" s="48">
         <v>46203</v>
       </c>
-      <c r="D54" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F54" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G54" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H54" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I54" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J54" s="46">
+      <c r="D54" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G54" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I54" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J54" s="47">
         <v>21</v>
       </c>
-      <c r="K54" s="46" t="s">
+      <c r="K54" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:11">
-      <c r="A55" s="46" t="s">
+      <c r="A55" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="48">
         <v>46203</v>
       </c>
-      <c r="D55" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="G55" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H55" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I55" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J55" s="46">
+      <c r="D55" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G55" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H55" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I55" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J55" s="47">
         <v>21</v>
       </c>
-      <c r="K55" s="46" t="s">
+      <c r="K55" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:11">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C56" s="47">
+      <c r="C56" s="48">
         <v>46203</v>
       </c>
-      <c r="D56" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G56" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H56" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I56" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J56" s="46">
+      <c r="D56" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G56" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I56" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J56" s="47">
         <v>18</v>
       </c>
-      <c r="K56" s="46" t="s">
+      <c r="K56" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:11">
-      <c r="A57" s="46" t="s">
+      <c r="A57" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="47">
+      <c r="C57" s="48">
         <v>46203</v>
       </c>
-      <c r="D57" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E57" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F57" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G57" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H57" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I57" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J57" s="46">
+      <c r="D57" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" s="47">
         <v>20</v>
       </c>
-      <c r="K57" s="46" t="s">
+      <c r="K57" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:11">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C58" s="47">
+      <c r="C58" s="48">
         <v>46203</v>
       </c>
-      <c r="D58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="F58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="H58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="J58" s="46">
+      <c r="D58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" s="47">
         <v>12</v>
       </c>
-      <c r="K58" s="46" t="s">
+      <c r="K58" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:11">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <v>46203</v>
       </c>
-      <c r="D59" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G59" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H59" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I59" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J59" s="46">
+      <c r="D59" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G59" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I59" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J59" s="47">
         <v>19</v>
       </c>
-      <c r="K59" s="46" t="s">
+      <c r="K59" s="47" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="60" ht="18" spans="1:11">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="46" t="s">
+      <c r="B60" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <v>46203</v>
       </c>
-      <c r="D60" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F60" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G60" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H60" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J60" s="46">
+      <c r="D60" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J60" s="47">
         <v>15</v>
       </c>
-      <c r="K60" s="46" t="s">
+      <c r="K60" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:11">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="46" t="s">
+      <c r="B61" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <v>46203</v>
       </c>
-      <c r="D61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="I61" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="J61" s="46">
+      <c r="D61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="I61" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" s="47">
         <v>18</v>
       </c>
-      <c r="K61" s="46" t="s">
+      <c r="K61" s="47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="62" ht="18" spans="1:11">
-      <c r="A62" s="46" t="s">
+      <c r="A62" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B62" s="46" t="s">
+      <c r="B62" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <v>46203</v>
       </c>
-      <c r="D62" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E62" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F62" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="G62" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="H62" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="I62" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="J62" s="46">
+      <c r="D62" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J62" s="47">
         <v>20</v>
       </c>
-      <c r="K62" s="46" t="s">
+      <c r="K62" s="47" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4823,558 +4826,558 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:13">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="33" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:13">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="34">
         <v>45382</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <v>45473</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <v>45565</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <v>45657</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="34">
         <v>45747</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>45838</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="29">
         <v>45930</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="29">
         <v>46022</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="34">
         <v>46112</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="29">
         <v>46203</v>
       </c>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
     </row>
     <row r="3" ht="18" spans="1:13">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="36">
         <v>102</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="37">
         <v>95</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="37">
         <v>93</v>
       </c>
-      <c r="E3" s="36">
+      <c r="E3" s="37">
         <v>102</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="37">
         <v>100</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="37">
         <v>105</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="38">
         <v>104</v>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="38">
         <v>102</v>
       </c>
-      <c r="J3" s="37">
+      <c r="J3" s="38">
         <v>90</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="39">
         <v>99</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="41"/>
     </row>
     <row r="4" ht="18" spans="1:13">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="41">
+      <c r="B4" s="42">
         <v>105</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C4" s="43">
         <v>106</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="43">
         <v>103</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="43">
         <v>104</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="43">
         <v>105</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="43">
         <v>102</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="43">
         <v>100</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="43">
         <v>100</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="43">
         <v>90</v>
       </c>
-      <c r="K4" s="43">
+      <c r="K4" s="44">
         <v>99</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="41"/>
     </row>
     <row r="5" ht="18" spans="1:13">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="42">
         <v>100</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="43">
         <v>96</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="43">
         <v>100</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <v>102</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="43">
         <v>100</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="43">
         <v>103</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="43">
         <v>105</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="43">
         <v>103</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="43">
         <v>102</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="44">
         <v>102</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="41"/>
     </row>
     <row r="6" ht="18" spans="1:13">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="42">
         <v>100</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="43">
         <v>91</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="43">
         <v>100</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="43">
         <v>100</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="43">
         <v>96</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="43">
         <v>91</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="43">
         <v>96</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="43">
         <v>92</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="43">
         <v>100</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="44">
         <v>100</v>
       </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="41"/>
     </row>
     <row r="7" ht="18" spans="1:13">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="42">
         <v>100</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="43">
         <v>100</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>100</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="43">
         <v>100</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="43">
         <v>100</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="43">
         <v>101</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="43">
         <v>102</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="43">
         <v>101</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="43">
         <v>102</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="45">
         <v>98</v>
       </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="41"/>
     </row>
     <row r="8" ht="18" spans="1:13">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="42">
         <v>102.5</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="43">
         <v>104</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <v>105</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="43">
         <v>101</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="43">
         <v>103</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="43">
         <v>102</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="43">
         <v>101</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="43">
         <v>102</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="43">
         <v>103.5</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="45">
         <v>104</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="41"/>
     </row>
     <row r="9" ht="18" spans="1:13">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="42">
         <v>98</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="43">
         <v>100</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <v>96</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="43">
         <v>100</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="43">
         <v>101</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="43">
         <v>100</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="43">
         <v>100</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="43">
         <v>100</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="43">
         <v>100</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="45">
         <v>101</v>
       </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="41"/>
     </row>
     <row r="10" ht="18" spans="1:13">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="42">
         <v>100</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="43">
         <v>105</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <v>105</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <v>100</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="43">
         <v>104</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="43">
         <v>102</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="43">
         <v>101</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="43">
         <v>100</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="43">
         <v>90</v>
       </c>
-      <c r="K10" s="44">
+      <c r="K10" s="45">
         <v>100</v>
       </c>
-      <c r="L10" s="39"/>
-      <c r="M10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="41"/>
     </row>
     <row r="11" ht="18" spans="1:13">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="42">
         <v>95</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="43">
         <v>94</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <v>88</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="43">
         <v>83.5</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="43">
         <v>91</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="43">
         <v>88.5</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="43">
         <v>83.5</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="43">
         <v>86.5</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="43">
         <v>100</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="45">
         <v>100</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="41"/>
     </row>
     <row r="12" ht="18" spans="1:13">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="42"/>
+      <c r="C12" s="43">
         <v>103</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <v>106</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <v>106</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="43">
         <v>106</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>98</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="43">
         <v>100</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="43">
         <v>100</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="43">
         <v>101</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <v>102</v>
       </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="41"/>
     </row>
     <row r="13" ht="18" spans="1:13">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42">
+      <c r="B13" s="42"/>
+      <c r="C13" s="43">
         <v>95</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <v>101</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="43">
         <v>100</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="43">
         <v>96</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="43">
         <v>103</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="43">
         <v>102</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="43">
         <v>99</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="43">
         <v>102</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="45">
         <v>101</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="41"/>
     </row>
     <row r="14" ht="18" spans="1:13">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42">
+      <c r="B14" s="42"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43">
         <v>96</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="43">
         <v>101</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="43">
         <v>101</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="43">
         <v>103</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="43">
         <v>103</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="43">
         <v>102.5</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="45">
         <v>101.4</v>
       </c>
-      <c r="L14" s="39"/>
-      <c r="M14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="41"/>
     </row>
     <row r="15" ht="18" spans="1:13">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42">
+      <c r="B15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43">
         <v>100</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="44">
         <v>96.4</v>
       </c>
-      <c r="L15" s="39"/>
-      <c r="M15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="41"/>
     </row>
     <row r="16" ht="18" spans="1:13">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42">
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43">
         <v>100</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="44">
         <v>100</v>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5388,210 +5391,210 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9.23076923076923" style="26"/>
-    <col min="2" max="2" width="11.6923076923077" style="26" customWidth="1"/>
-    <col min="3" max="3" width="12.9230769230769" style="26" customWidth="1"/>
-    <col min="4" max="4" width="10.5384615384615" style="26" customWidth="1"/>
-    <col min="5" max="5" width="12.9230769230769" style="26" customWidth="1"/>
-    <col min="6" max="6" width="11.6923076923077" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="9.23076923076923" style="26"/>
+    <col min="1" max="1" width="9.23076923076923" style="27"/>
+    <col min="2" max="2" width="11.6923076923077" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.9230769230769" style="27" customWidth="1"/>
+    <col min="4" max="4" width="10.5384615384615" style="27" customWidth="1"/>
+    <col min="5" max="5" width="12.9230769230769" style="27" customWidth="1"/>
+    <col min="6" max="6" width="11.6923076923077" style="27" customWidth="1"/>
+    <col min="7" max="16384" width="9.23076923076923" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" s="26" customFormat="1" ht="18" spans="1:6">
-      <c r="A1" s="16" t="s">
+    <row r="1" s="27" customFormat="1" ht="18" spans="1:6">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="28" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" s="26" customFormat="1" ht="18" spans="1:6">
-      <c r="A2" s="16" t="s">
+    <row r="2" s="27" customFormat="1" ht="18" spans="1:6">
+      <c r="A2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="29">
         <v>45473</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <v>45657</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <v>45838</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <v>46022</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <v>46203</v>
       </c>
     </row>
-    <row r="3" s="26" customFormat="1" spans="1:6">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="27" customFormat="1" spans="1:6">
+      <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-    </row>
-    <row r="4" s="26" customFormat="1" spans="1:6">
-      <c r="A4" s="16" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+    </row>
+    <row r="4" s="27" customFormat="1" spans="1:6">
+      <c r="A4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-    </row>
-    <row r="5" s="26" customFormat="1" spans="1:6">
-      <c r="A5" s="16" t="s">
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+    </row>
+    <row r="5" s="27" customFormat="1" spans="1:6">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-    </row>
-    <row r="6" s="26" customFormat="1" spans="1:6">
-      <c r="A6" s="16" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" s="27" customFormat="1" spans="1:6">
+      <c r="A6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-    </row>
-    <row r="7" s="26" customFormat="1" spans="1:6">
-      <c r="A7" s="16" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+    </row>
+    <row r="7" s="27" customFormat="1" spans="1:6">
+      <c r="A7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" s="26" customFormat="1" spans="1:6">
-      <c r="A8" s="16" t="s">
+    <row r="8" s="27" customFormat="1" spans="1:6">
+      <c r="A8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-    </row>
-    <row r="9" s="26" customFormat="1" spans="1:6">
-      <c r="A9" s="16" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" s="27" customFormat="1" spans="1:6">
+      <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="29"/>
-    </row>
-    <row r="10" s="26" customFormat="1" spans="1:6">
-      <c r="A10" s="16" t="s">
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" s="27" customFormat="1" spans="1:6">
+      <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="29"/>
-    </row>
-    <row r="11" s="26" customFormat="1" spans="1:6">
-      <c r="A11" s="16" t="s">
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" s="27" customFormat="1" spans="1:6">
+      <c r="A11" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-    </row>
-    <row r="12" s="26" customFormat="1" spans="1:6">
-      <c r="A12" s="16" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+    </row>
+    <row r="12" s="27" customFormat="1" spans="1:6">
+      <c r="A12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-    </row>
-    <row r="13" s="26" customFormat="1" spans="1:6">
-      <c r="A13" s="16" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+    </row>
+    <row r="13" s="27" customFormat="1" spans="1:6">
+      <c r="A13" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" s="26" customFormat="1" spans="1:6">
-      <c r="A14" s="16" t="s">
+    <row r="14" s="27" customFormat="1" spans="1:6">
+      <c r="A14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-    </row>
-    <row r="15" s="26" customFormat="1" spans="1:6">
-      <c r="A15" s="16" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" s="27" customFormat="1" spans="1:6">
+      <c r="A15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-    </row>
-    <row r="16" s="26" customFormat="1" spans="1:6">
-      <c r="A16" s="16" t="s">
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" s="27" customFormat="1" spans="1:6">
+      <c r="A16" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5611,136 +5614,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16"/>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="24">
         <v>44393</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="24">
         <v>45488</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="24">
         <v>44393</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <v>45489</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <v>46583</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>45489</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <v>45464</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>46558</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>45464</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:4">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>45474</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>46568</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>45474</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>45478</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>46572</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>45478</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>45618</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>46712</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>45618</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:4">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>46131</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>47226</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>46131</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>46174</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>47269</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>46174</v>
       </c>
     </row>
@@ -5760,21 +5763,21 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17.6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.2980769230769" style="9" customWidth="1"/>
-    <col min="2" max="2" width="19.3846153846154" style="9" customWidth="1"/>
-    <col min="3" max="3" width="67.3076923076923" style="9" customWidth="1"/>
-    <col min="4" max="4" width="52.3942307692308" style="9" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="9"/>
+    <col min="1" max="1" width="17.2980769230769" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19.3846153846154" style="11" customWidth="1"/>
+    <col min="3" max="3" width="67.3076923076923" style="11" customWidth="1"/>
+    <col min="4" max="4" width="52.3942307692308" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="9.23076923076923" style="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D1" s="11" t="s">
@@ -5782,142 +5785,142 @@
       </c>
     </row>
     <row r="2" ht="18" spans="1:4">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>46233</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>46233</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>46233</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>46233</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:4">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>46233</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>46233</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>46233</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:4">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>46233</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:4">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>46233</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>46233</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="11" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5930,14 +5933,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12.0769230769231" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="18" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -5956,7 +5959,7 @@
       </c>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="18" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="18" spans="1:16">
       <c r="A2" s="2" t="s">
         <v>85</v>
       </c>
@@ -5985,7 +5988,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:9">
+    <row r="3" ht="18" spans="1:16">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -6014,7 +6017,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:9">
+    <row r="4" ht="18" spans="1:16">
       <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
@@ -6043,7 +6046,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" ht="18" spans="1:9">
+    <row r="5" ht="18" spans="1:16">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -6072,7 +6075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="1:9">
+    <row r="6" ht="18" spans="1:16">
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
@@ -6101,7 +6104,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:9">
+    <row r="7" ht="18" spans="1:16">
       <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
@@ -6130,7 +6133,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="1:9">
+    <row r="8" ht="18" spans="1:16">
       <c r="A8" s="7" t="s">
         <v>30</v>
       </c>
@@ -6159,7 +6162,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" ht="18" spans="1:9">
+    <row r="9" ht="18" spans="1:16">
       <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
@@ -6188,7 +6191,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" ht="18" spans="1:9">
+    <row r="10" ht="18" spans="1:16">
       <c r="A10" s="7" t="s">
         <v>31</v>
       </c>
@@ -6204,8 +6207,13 @@
       <c r="I10" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" ht="18" spans="1:9">
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" ht="18" spans="1:16">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
@@ -6233,8 +6241,13 @@
       <c r="I11" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" ht="18" spans="1:9">
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" ht="18.75" spans="1:16">
       <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
@@ -6262,8 +6275,13 @@
       <c r="I12" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" ht="18" spans="1:9">
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" ht="18.75" spans="1:16">
       <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
@@ -6291,8 +6309,13 @@
       <c r="I13" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" ht="18" spans="1:9">
+      <c r="L13" s="8"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row r="14" ht="18.75" spans="1:16">
       <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
@@ -6320,8 +6343,13 @@
       <c r="I14" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" ht="18" spans="1:9">
+      <c r="L14" s="8"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" ht="18" spans="1:16">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
@@ -6349,8 +6377,13 @@
       <c r="I15" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="16" ht="18" spans="1:9">
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" ht="18" spans="1:16">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -6360,12 +6393,17 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="10" t="s">
         <v>94</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>90</v>
       </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
